--- a/resources/modele_bilan.xlsx
+++ b/resources/modele_bilan.xlsx
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="E8">
-        <f>CtaCptSoldeNm1("201*","209*")</f>
+        <f>CtaCptSoldeNm1("201*","209*")-(-CtaCptSoldeNm1("280*")-CtaCptSoldeNm1("290*"))</f>
         <v/>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v/>
       </c>
       <c r="E9">
-        <f>CtaCptSoldeNm1("21*")</f>
+        <f>CtaCptSoldeNm1("21*")-(-CtaCptSoldeNm1("281*")-CtaCptSoldeNm1("291*"))</f>
         <v/>
       </c>
       <c r="F9" t="inlineStr">
@@ -578,7 +578,7 @@
         <v/>
       </c>
       <c r="E10">
-        <f>CtaCptSoldeNm1("22*")</f>
+        <f>CtaCptSoldeNm1("22*")-(-CtaCptSoldeNm1("282*")-CtaCptSoldeNm1("292*"))</f>
         <v/>
       </c>
       <c r="F10" t="inlineStr">
@@ -614,7 +614,7 @@
         <v/>
       </c>
       <c r="E11">
-        <f>CtaCptSoldeNm1("231*","233*")</f>
+        <f>CtaCptSoldeNm1("231*","233*")-(-CtaCptSoldeNm1("2831*","2833*")-CtaCptSoldeNm1("2931*","2933*"))</f>
         <v/>
       </c>
       <c r="F11" t="inlineStr">
@@ -650,7 +650,7 @@
         <v/>
       </c>
       <c r="E12">
-        <f>CtaCptSoldeNm1("234*","239*")</f>
+        <f>CtaCptSoldeNm1("234*","239*")-(-CtaCptSoldeNm1("2834*","2839*")-CtaCptSoldeNm1("2934*","2939*"))</f>
         <v/>
       </c>
       <c r="F12" t="inlineStr">
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E13">
-        <f>CtaCptSoldeNm1("240*","244*")</f>
+        <f>CtaCptSoldeNm1("240*","244*")-(-CtaCptSoldeNm1("2840*","2844*")-CtaCptSoldeNm1("2940*","2944*"))</f>
         <v/>
       </c>
       <c r="F13" t="inlineStr">
@@ -714,7 +714,7 @@
         <v/>
       </c>
       <c r="E14">
-        <f>CtaCptSoldeNm1("245*")</f>
+        <f>CtaCptSoldeNm1("245*")-(-CtaCptSoldeNm1("2845*","2849*")-CtaCptSoldeNm1("2945*","2949*"))</f>
         <v/>
       </c>
       <c r="F14" t="inlineStr">
@@ -726,6 +726,10 @@
         <f>[R150.EtLoc]=-CtaCptSolde("7*")-CtaCptSolde("6*")</f>
         <v/>
       </c>
+      <c r="H14">
+        <f>-CtaCptSoldeNm1("7*")-CtaCptSoldeNm1("6*")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -746,7 +750,7 @@
         <v/>
       </c>
       <c r="E15">
-        <f>CtaCptSoldeNm1("25*")</f>
+        <f>CtaCptSoldeNm1("25*")-(-CtaCptSoldeNm1("2850*","2859*")-CtaCptSoldeNm1("2950*","2959*"))</f>
         <v/>
       </c>
       <c r="F15" t="inlineStr">
@@ -782,7 +786,7 @@
         <v/>
       </c>
       <c r="E16">
-        <f>CtaCptSoldeNm1("26*")+CtaCptSoldeNm1("27*")</f>
+        <f>CtaCptSoldeNm1("26*")+CtaCptSoldeNm1("27*")-(-CtaCptSoldeNm1("2860*","2869*")-CtaCptSoldeNm1("2960*","2969*"))</f>
         <v/>
       </c>
       <c r="F16" t="inlineStr">
@@ -889,7 +893,7 @@
         <v/>
       </c>
       <c r="E20">
-        <f>CtaCptSoldeDébitNm1("31*")-CtaCptSoldeCréditNm1("3*","39*")</f>
+        <f>CtaCptSoldeDébitNm1("31*")</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1337,7 @@
         <v/>
       </c>
       <c r="E37">
-        <f>CtaCptSoldeDébitNm1("201*","59*")-CtaCptSoldeDébitNm1("28*","29*")</f>
+        <f>CtaCptSoldeNm1("20*","27*")-(-CtaCptSoldeNm1("280*","2869*")-CtaCptSoldeNm1("290*","2969*"))+CtaCptSoldeDébitNm1("3*","39*")-CtaCptSoldeCréditNm1("3*","39*")+CtaCptSoldeDébitNm1("4*","59*")</f>
         <v/>
       </c>
       <c r="F37" t="inlineStr">

--- a/resources/modele_bilan.xlsx
+++ b/resources/modele_bilan.xlsx
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D37">
-        <f>CtaCptSoldeDébit("201*","59*")-(-CtaCptSolde("280*","2869*")-CtaCptSolde("290*","2969*"))</f>
+        <f>CtaCptSolde("20*","27*")-(-CtaCptSolde("280*","2869*")-CtaCptSolde("290*","2969*"))+CtaCptSoldeDébit("3*","39*")-CtaCptSoldeCrédit("3*","39*")+CtaCptSoldeDébit("4*","59*")</f>
         <v/>
       </c>
       <c r="E37">
